--- a/data/trans_dic/IP09B01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 67,82</t>
+          <t>17,13; 69,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,99; 65,7</t>
+          <t>28,36; 64,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 59,07</t>
+          <t>15,07; 59,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,05; 80,78</t>
+          <t>25,63; 78,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,15; 64,41</t>
+          <t>19,93; 61,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,16; 55,43</t>
+          <t>21,14; 54,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,82; 75,11</t>
+          <t>31,78; 74,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,99; 77,84</t>
+          <t>29,87; 77,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,05; 58,99</t>
+          <t>26,76; 60,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,9; 55,36</t>
+          <t>29,06; 54,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,53; 60,95</t>
+          <t>28,84; 61,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,78; 72,78</t>
+          <t>36,94; 71,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,04; 93,14</t>
+          <t>64,49; 92,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,56; 88,91</t>
+          <t>63,84; 89,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,2; 79,19</t>
+          <t>45,49; 79,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,95; 90,8</t>
+          <t>47,21; 91,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,99; 90,61</t>
+          <t>67,91; 89,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,22; 78,9</t>
+          <t>54,08; 79,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,4; 78,94</t>
+          <t>43,54; 78,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,06; 77,2</t>
+          <t>45,75; 79,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71,88; 88,41</t>
+          <t>71,27; 88,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,9; 81,13</t>
+          <t>62,58; 81,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,24; 75,08</t>
+          <t>49,62; 75,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,89; 78,8</t>
+          <t>52,58; 79,23</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,73; 74,28</t>
+          <t>33,62; 75,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,61; 76,2</t>
+          <t>39,0; 75,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,36; 82,49</t>
+          <t>23,75; 80,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58,61; 94,91</t>
+          <t>57,41; 95,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,91; 87,05</t>
+          <t>49,83; 86,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,28; 86,31</t>
+          <t>48,43; 86,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,57; 100,0</t>
+          <t>35,77; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,59; 82,99</t>
+          <t>43,01; 81,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,2; 77,64</t>
+          <t>49,08; 77,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,04; 75,65</t>
+          <t>48,33; 74,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,94; 79,93</t>
+          <t>36,88; 80,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,58; 84,43</t>
+          <t>57,29; 83,01</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,8; 92,06</t>
+          <t>35,69; 92,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,3; 86,56</t>
+          <t>45,19; 86,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,82; 82,7</t>
+          <t>32,04; 82,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,83; 91,93</t>
+          <t>61,69; 91,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,62; 73,59</t>
+          <t>36,57; 75,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,71; 82,44</t>
+          <t>53,73; 85,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,53; 64,53</t>
+          <t>19,55; 68,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,27; 92,03</t>
+          <t>61,81; 91,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,98; 75,25</t>
+          <t>43,77; 73,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,95; 80,86</t>
+          <t>57,48; 82,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,12; 68,87</t>
+          <t>34,46; 68,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,13; 88,64</t>
+          <t>67,09; 89,03</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,32; 74,63</t>
+          <t>53,79; 76,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,68; 73,21</t>
+          <t>56,49; 73,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,92; 66,39</t>
+          <t>43,48; 67,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,69; 83,67</t>
+          <t>65,19; 84,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,47; 75,05</t>
+          <t>58,46; 74,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,12; 70,26</t>
+          <t>52,57; 69,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,52; 68,46</t>
+          <t>44,39; 69,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>59,11; 79,0</t>
+          <t>58,95; 79,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,18; 73,77</t>
+          <t>59,94; 73,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,92; 68,92</t>
+          <t>57,16; 69,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,09; 63,67</t>
+          <t>48,02; 63,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,47; 79,49</t>
+          <t>65,01; 78,91</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3905</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9654</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5456</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17724</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10082</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10707</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1599; 6451</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5780; 13051</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1459; 5784</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2095; 6424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2699; 8270</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4591; 11898</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4015; 9378</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3419; 8924</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6123; 13730</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12234; 22802</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6434; 13792</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>7249; 14085</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>19139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22501</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11909</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6711</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28532</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25942</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14575</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>47671</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48444</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25021</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>21285</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>15354; 21934</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18060; 25250</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8422; 14737</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4387; 8500</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23863; 31304</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20779; 30636</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9174; 16617</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10367; 17932</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>42012; 52185</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>41746; 54400</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>19643; 30038</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>16799; 25315</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11880</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13643</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10914</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10195</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4404</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>15375</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>18312</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22075</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8761</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>29018</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4605; 10349</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7877; 15295</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1990; 6771</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9609; 15900</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7494; 13053</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7245; 12962</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2121; 5931</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10078; 19196</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>14105; 22260</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16994; 26336</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5278; 11575</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>23012; 33341</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5310</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6433</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23261</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16531</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5038</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>32377</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15316</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26044</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11471</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>55638</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2810; 7247</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6045; 11528</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3378; 8680</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>18105; 26924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6499; 13336</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>12601; 20017</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2310; 8079</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>25648; 37947</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11223; 18816</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>21169; 30202</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7705; 15276</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>47523; 63064</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>53548</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>48125</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>68522</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>90659</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>114287</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>55336</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>116648</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>29434; 41587</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46455; 60424</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20490; 31947</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>41428; 53707</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>47642; 60804</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>51812; 68059</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22837; 35626</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>58373; 79100</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>81647; 99940</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>103352; 125068</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>47336; 62952</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>105685; 128287</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 69,1</t>
+          <t>14,56; 68,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,36; 64,03</t>
+          <t>28,15; 65,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 59,74</t>
+          <t>15,58; 59,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,63; 78,6</t>
+          <t>29,07; 82,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,93; 61,07</t>
+          <t>19,81; 61,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,14; 54,77</t>
+          <t>20,51; 54,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,78; 74,25</t>
+          <t>28,16; 74,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,87; 77,95</t>
+          <t>31,86; 77,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,76; 60,01</t>
+          <t>25,69; 56,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,06; 54,16</t>
+          <t>30,19; 54,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 61,81</t>
+          <t>29,77; 61,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,94; 71,78</t>
+          <t>35,82; 70,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,49; 92,13</t>
+          <t>63,66; 91,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,84; 89,26</t>
+          <t>63,92; 88,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,49; 79,59</t>
+          <t>46,16; 81,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,21; 91,48</t>
+          <t>40,79; 89,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,91; 89,08</t>
+          <t>68,42; 90,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,08; 79,74</t>
+          <t>52,71; 80,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,54; 78,87</t>
+          <t>42,97; 79,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,75; 79,14</t>
+          <t>46,95; 78,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71,27; 88,53</t>
+          <t>71,25; 87,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,58; 81,55</t>
+          <t>62,66; 81,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49,62; 75,88</t>
+          <t>50,42; 74,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,58; 79,23</t>
+          <t>53,83; 79,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,62; 75,54</t>
+          <t>29,76; 74,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,0; 75,72</t>
+          <t>40,86; 75,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,75; 80,81</t>
+          <t>22,91; 80,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,41; 95,0</t>
+          <t>57,51; 95,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,83; 86,8</t>
+          <t>48,69; 87,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,43; 86,64</t>
+          <t>47,15; 86,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,77; 100,0</t>
+          <t>35,63; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,01; 81,93</t>
+          <t>44,44; 82,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,08; 77,46</t>
+          <t>48,35; 78,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,33; 74,9</t>
+          <t>48,01; 75,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36,88; 80,89</t>
+          <t>39,37; 80,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,29; 83,01</t>
+          <t>57,8; 83,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,69; 92,04</t>
+          <t>34,29; 92,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,19; 86,19</t>
+          <t>50,32; 89,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,04; 82,31</t>
+          <t>31,5; 83,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,69; 91,75</t>
+          <t>63,83; 91,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,57; 75,05</t>
+          <t>37,34; 74,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,73; 85,36</t>
+          <t>53,49; 84,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 68,37</t>
+          <t>17,83; 68,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,81; 91,46</t>
+          <t>61,5; 92,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,77; 73,38</t>
+          <t>44,49; 75,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,48; 82,01</t>
+          <t>56,37; 81,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,46; 68,32</t>
+          <t>32,1; 67,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,09; 89,03</t>
+          <t>66,34; 88,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,79; 76,0</t>
+          <t>54,79; 75,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,49; 73,47</t>
+          <t>56,48; 72,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,48; 67,8</t>
+          <t>43,74; 66,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,19; 84,51</t>
+          <t>65,62; 84,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,46; 74,61</t>
+          <t>59,33; 75,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,57; 69,06</t>
+          <t>53,37; 69,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,39; 69,25</t>
+          <t>46,18; 68,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,95; 79,88</t>
+          <t>58,71; 79,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,94; 73,37</t>
+          <t>60,06; 72,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,16; 69,18</t>
+          <t>57,1; 68,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,02; 63,87</t>
+          <t>48,12; 64,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,01; 78,91</t>
+          <t>65,01; 80,01</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1599; 6451</t>
+          <t>1359; 6350</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5780; 13051</t>
+          <t>5737; 13265</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1459; 5784</t>
+          <t>1508; 5751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2095; 6424</t>
+          <t>2376; 6735</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2699; 8270</t>
+          <t>2683; 8285</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4591; 11898</t>
+          <t>4455; 11830</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4015; 9378</t>
+          <t>3556; 9465</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3419; 8924</t>
+          <t>3648; 8821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6123; 13730</t>
+          <t>5877; 12971</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12234; 22802</t>
+          <t>12710; 23067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6434; 13792</t>
+          <t>6643; 13809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7249; 14085</t>
+          <t>7029; 13774</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15354; 21934</t>
+          <t>15156; 21664</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18060; 25250</t>
+          <t>18080; 25119</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8422; 14737</t>
+          <t>8548; 15108</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4387; 8500</t>
+          <t>3790; 8332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23863; 31304</t>
+          <t>24045; 31874</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20779; 30636</t>
+          <t>20251; 31026</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9174; 16617</t>
+          <t>9054; 16732</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10367; 17932</t>
+          <t>10639; 17689</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42012; 52185</t>
+          <t>41999; 51734</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41746; 54400</t>
+          <t>41797; 54393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19643; 30038</t>
+          <t>19960; 29578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16799; 25315</t>
+          <t>17199; 25554</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4605; 10349</t>
+          <t>4077; 10223</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7877; 15295</t>
+          <t>8253; 15332</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1990; 6771</t>
+          <t>1920; 6742</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9609; 15900</t>
+          <t>9627; 15901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7494; 13053</t>
+          <t>7322; 13161</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7245; 12962</t>
+          <t>7055; 12876</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2121; 5931</t>
+          <t>2113; 5931</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10078; 19196</t>
+          <t>10413; 19400</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14105; 22260</t>
+          <t>13895; 22515</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16994; 26336</t>
+          <t>16879; 26452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5278; 11575</t>
+          <t>5634; 11568</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23012; 33341</t>
+          <t>23215; 33637</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2810; 7247</t>
+          <t>2700; 7255</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6045; 11528</t>
+          <t>6730; 11991</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3378; 8680</t>
+          <t>3322; 8805</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18105; 26924</t>
+          <t>18730; 26968</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6499; 13336</t>
+          <t>6635; 13190</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12601; 20017</t>
+          <t>12545; 19788</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2310; 8079</t>
+          <t>2107; 8068</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25648; 37947</t>
+          <t>25519; 38274</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11223; 18816</t>
+          <t>11408; 19329</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21169; 30202</t>
+          <t>20760; 29917</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7705; 15276</t>
+          <t>7179; 15015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47523; 63064</t>
+          <t>46997; 62916</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29434; 41587</t>
+          <t>29982; 41303</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46455; 60424</t>
+          <t>46450; 59996</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20490; 31947</t>
+          <t>20610; 31256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41428; 53707</t>
+          <t>41701; 53764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47642; 60804</t>
+          <t>48345; 61351</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51812; 68059</t>
+          <t>52596; 68499</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22837; 35626</t>
+          <t>23760; 35233</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58373; 79100</t>
+          <t>58136; 79103</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81647; 99940</t>
+          <t>81807; 99351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103352; 125068</t>
+          <t>103227; 124300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47336; 62952</t>
+          <t>47433; 63783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>105685; 128287</t>
+          <t>105698; 130081</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40,29%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>41,82%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>47,37%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>34,25%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>55,2%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,56%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 68,01</t>
+          <t>20,15; 64,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,15; 65,08</t>
+          <t>21,16; 55,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,58; 59,4</t>
+          <t>29,82; 75,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,07; 82,4</t>
+          <t>31,79; 79,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,81; 61,18</t>
+          <t>18,4; 67,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,51; 54,46</t>
+          <t>29,99; 65,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,16; 74,93</t>
+          <t>15,51; 59,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,86; 77,05</t>
+          <t>26,39; 81,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,69; 56,7</t>
+          <t>23,05; 58,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,19; 54,79</t>
+          <t>30,9; 55,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,77; 61,89</t>
+          <t>29,53; 60,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,82; 70,2</t>
+          <t>38,84; 74,2</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>67,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66,44%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>80,39%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>79,54%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>64,32%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>72,22%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>81,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>62,23%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,21%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,66; 91,0</t>
+          <t>67,99; 90,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,92; 88,8</t>
+          <t>53,22; 78,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,16; 81,6</t>
+          <t>43,4; 78,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,79; 89,66</t>
+          <t>48,67; 79,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,42; 90,7</t>
+          <t>64,04; 93,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,71; 80,75</t>
+          <t>65,56; 88,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,97; 79,41</t>
+          <t>44,2; 79,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,95; 78,07</t>
+          <t>37,36; 89,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>71,25; 87,76</t>
+          <t>71,88; 88,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62,66; 81,54</t>
+          <t>62,9; 81,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,42; 74,72</t>
+          <t>50,24; 75,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,83; 79,98</t>
+          <t>52,7; 79,21</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72,58%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>68,14%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74,26%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>54,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>58,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>51,99%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,26%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,76; 74,63</t>
+          <t>50,91; 87,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,86; 75,91</t>
+          <t>46,28; 86,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,91; 80,46</t>
+          <t>35,57; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,51; 95,0</t>
+          <t>48,09; 83,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,69; 87,52</t>
+          <t>31,73; 74,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,15; 86,06</t>
+          <t>40,61; 76,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,63; 100,0</t>
+          <t>23,36; 82,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,44; 82,8</t>
+          <t>57,47; 94,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48,35; 78,35</t>
+          <t>47,2; 77,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,01; 75,23</t>
+          <t>49,04; 75,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,37; 80,84</t>
+          <t>37,94; 79,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,8; 83,74</t>
+          <t>60,22; 85,42</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76,24%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>67,43%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>71,13%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>61,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>79,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,64%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>34,29; 92,13</t>
+          <t>37,62; 73,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,32; 89,65</t>
+          <t>50,71; 82,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,5; 83,5</t>
+          <t>18,53; 64,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,83; 91,9</t>
+          <t>59,34; 90,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,34; 74,23</t>
+          <t>38,8; 92,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,49; 84,38</t>
+          <t>46,3; 86,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,83; 68,28</t>
+          <t>34,82; 82,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,5; 92,24</t>
+          <t>56,11; 87,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,49; 75,38</t>
+          <t>42,98; 75,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,37; 81,24</t>
+          <t>56,95; 80,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,1; 67,15</t>
+          <t>34,12; 68,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,34; 88,82</t>
+          <t>63,92; 86,33</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>65,34%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>65,11%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>54,79; 75,48</t>
+          <t>58,47; 75,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,48; 72,95</t>
+          <t>54,12; 70,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,74; 66,33</t>
+          <t>45,52; 68,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,62; 84,6</t>
+          <t>60,48; 79,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,33; 75,29</t>
+          <t>54,32; 74,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,37; 69,5</t>
+          <t>55,68; 73,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,18; 68,48</t>
+          <t>42,92; 66,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,71; 79,88</t>
+          <t>63,28; 81,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,06; 72,94</t>
+          <t>60,18; 73,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57,1; 68,75</t>
+          <t>56,92; 68,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,12; 64,71</t>
+          <t>47,09; 63,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,01; 80,01</t>
+          <t>64,01; 78,34</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5456</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3905</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>9654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3316</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8070</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6765</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>9625</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1359; 6350</t>
+          <t>2729; 8722</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5737; 13265</t>
+          <t>4596; 12040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1508; 5751</t>
+          <t>3766; 9487</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2376; 6735</t>
+          <t>2989; 7503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2683; 8285</t>
+          <t>1717; 6331</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4455; 11830</t>
+          <t>6113; 13391</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3556; 9465</t>
+          <t>1502; 5720</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3648; 8821</t>
+          <t>2056; 6310</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5877; 12971</t>
+          <t>5274; 13496</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12710; 23067</t>
+          <t>13009; 23308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6643; 13809</t>
+          <t>6590; 13600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7029; 13774</t>
+          <t>6677; 12754</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28532</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25942</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12558</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19139</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22501</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11909</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6711</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28532</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25942</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13112</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>18678</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15156; 21664</t>
+          <t>23893; 31840</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18080; 25119</t>
+          <t>20446; 30314</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8548; 15108</t>
+          <t>9144; 16631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3790; 8332</t>
+          <t>9200; 14956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24045; 31874</t>
+          <t>15246; 22176</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20251; 31026</t>
+          <t>18545; 25152</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9054; 16732</t>
+          <t>8184; 14662</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10639; 17689</t>
+          <t>3321; 7925</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41999; 51734</t>
+          <t>42374; 52118</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41797; 54393</t>
+          <t>41958; 54122</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19960; 29578</t>
+          <t>19887; 29722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17199; 25554</t>
+          <t>14646; 22014</t>
         </is>
       </c>
     </row>
@@ -1925,32 +1925,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10914</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10195</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4404</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14585</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7398</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11880</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4357</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13643</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>10914</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10195</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4404</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29018</t>
+          <t>28407</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4077; 10223</t>
+          <t>7656; 13090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8253; 15332</t>
+          <t>6924; 12913</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1920; 6742</t>
+          <t>2110; 5931</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9627; 15901</t>
+          <t>10364; 17961</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7322; 13161</t>
+          <t>4347; 10175</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7055; 12876</t>
+          <t>8202; 15391</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2113; 5931</t>
+          <t>1957; 6912</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10413; 19400</t>
+          <t>9808; 16126</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13895; 22515</t>
+          <t>13564; 22310</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16879; 26452</t>
+          <t>17242; 26598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5634; 11568</t>
+          <t>5429; 11438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23215; 33637</t>
+          <t>23256; 32988</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10006</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16531</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5038</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29745</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5310</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9513</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6433</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23261</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10006</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16531</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5038</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32377</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55638</t>
+          <t>48671</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2700; 7255</t>
+          <t>6684; 13076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6730; 11991</t>
+          <t>11892; 19332</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3322; 8805</t>
+          <t>2190; 7625</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18730; 26968</t>
+          <t>23151; 35431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6635; 13190</t>
+          <t>3055; 7249</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12545; 19788</t>
+          <t>6193; 11578</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2107; 8068</t>
+          <t>3672; 8721</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25519; 38274</t>
+          <t>14217; 22219</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11408; 19329</t>
+          <t>11020; 19297</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20760; 29917</t>
+          <t>20974; 29777</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7179; 15015</t>
+          <t>7629; 15400</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46997; 62916</t>
+          <t>41133; 55559</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>53548</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>26016</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>54908</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>105380</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29982; 41303</t>
+          <t>47648; 61161</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46450; 59996</t>
+          <t>53340; 69245</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20610; 31256</t>
+          <t>23419; 35223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41701; 53764</t>
+          <t>53751; 70273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48345; 61351</t>
+          <t>29720; 40835</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52596; 68499</t>
+          <t>45792; 60211</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23760; 35233</t>
+          <t>20224; 31287</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58136; 79103</t>
+          <t>37389; 48108</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81807; 99351</t>
+          <t>81973; 100480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103227; 124300</t>
+          <t>102905; 124602</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47433; 63783</t>
+          <t>46415; 62759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>105698; 130081</t>
+          <t>94707; 115901</t>
         </is>
       </c>
     </row>
